--- a/STA01D.xlsx
+++ b/STA01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="279">
   <si>
     <t/>
   </si>
@@ -124,12 +124,6 @@
     <t>RHINO DIY KEYCHN ASS</t>
   </si>
   <si>
-    <t>20135296</t>
-  </si>
-  <si>
-    <t>RHINO KPOP CARD FRME</t>
-  </si>
-  <si>
     <t>20136548</t>
   </si>
   <si>
@@ -458,12 +452,6 @@
   </si>
   <si>
     <t>DELI CTTER 2022/2024</t>
-  </si>
-  <si>
-    <t>20123496</t>
-  </si>
-  <si>
-    <t>CRYLA CLRNG PACK</t>
   </si>
   <si>
     <t>20132577</t>
@@ -1252,7 +1240,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1557,7 +1545,7 @@
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>21</v>
@@ -1597,7 +1585,7 @@
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>21</v>
@@ -1617,7 +1605,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>21</v>
@@ -1637,7 +1625,7 @@
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>21</v>
@@ -1657,7 +1645,7 @@
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>21</v>
@@ -1677,7 +1665,7 @@
         <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>21</v>
@@ -1697,7 +1685,7 @@
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>21</v>
@@ -1705,10 +1693,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1717,18 +1705,18 @@
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1737,18 +1725,18 @@
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1757,7 +1745,7 @@
         <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>21</v>
@@ -1765,10 +1753,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1777,7 +1765,7 @@
         <v>10</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>21</v>
@@ -1785,10 +1773,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1797,30 +1785,30 @@
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1857,7 +1845,7 @@
         <v>17</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>21</v>
@@ -1877,7 +1865,7 @@
         <v>17</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>21</v>
@@ -1897,7 +1885,7 @@
         <v>17</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>21</v>
@@ -1917,7 +1905,7 @@
         <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>21</v>
@@ -1937,7 +1925,7 @@
         <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>21</v>
@@ -1957,7 +1945,7 @@
         <v>17</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>21</v>
@@ -1974,13 +1962,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2297,7 +2285,7 @@
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2317,10 +2305,10 @@
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2377,7 +2365,7 @@
         <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>21</v>
@@ -2400,7 +2388,7 @@
         <v>24</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2457,10 +2445,10 @@
         <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2597,10 +2585,10 @@
         <v>20</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2617,10 +2605,10 @@
         <v>20</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2637,10 +2625,10 @@
         <v>20</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2657,7 +2645,7 @@
         <v>20</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>21</v>
@@ -2677,7 +2665,7 @@
         <v>20</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>21</v>
@@ -2697,7 +2685,7 @@
         <v>20</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>21</v>
@@ -2717,7 +2705,7 @@
         <v>20</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>21</v>
@@ -2737,7 +2725,7 @@
         <v>20</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>21</v>
@@ -2757,7 +2745,7 @@
         <v>20</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>21</v>
@@ -2777,7 +2765,7 @@
         <v>20</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>21</v>
@@ -2797,7 +2785,7 @@
         <v>20</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>21</v>
@@ -2817,7 +2805,7 @@
         <v>20</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>21</v>
@@ -2837,7 +2825,7 @@
         <v>20</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>21</v>
@@ -2857,7 +2845,7 @@
         <v>20</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>21</v>
@@ -2877,7 +2865,7 @@
         <v>20</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>21</v>
@@ -2897,7 +2885,7 @@
         <v>20</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>21</v>
@@ -2917,10 +2905,10 @@
         <v>20</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2937,10 +2925,10 @@
         <v>20</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2957,10 +2945,10 @@
         <v>20</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2977,10 +2965,10 @@
         <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2997,7 +2985,7 @@
         <v>20</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>21</v>
@@ -3014,10 +3002,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>21</v>
@@ -3034,10 +3022,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>21</v>
@@ -3057,7 +3045,7 @@
         <v>24</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>21</v>
@@ -3077,7 +3065,7 @@
         <v>24</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>21</v>
@@ -3097,7 +3085,7 @@
         <v>24</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>21</v>
@@ -3117,7 +3105,7 @@
         <v>24</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>21</v>
@@ -3137,7 +3125,7 @@
         <v>24</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>21</v>
@@ -3157,7 +3145,7 @@
         <v>24</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>21</v>
@@ -3177,7 +3165,7 @@
         <v>24</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>21</v>
@@ -3197,7 +3185,7 @@
         <v>24</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>21</v>
@@ -3217,10 +3205,10 @@
         <v>24</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3234,10 +3222,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>21</v>
@@ -3254,13 +3242,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3277,7 +3265,7 @@
         <v>29</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>21</v>
@@ -3297,7 +3285,7 @@
         <v>29</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>21</v>
@@ -3317,7 +3305,7 @@
         <v>29</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>21</v>
@@ -3337,7 +3325,7 @@
         <v>29</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>21</v>
@@ -3357,10 +3345,10 @@
         <v>29</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3377,7 +3365,7 @@
         <v>29</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>21</v>
@@ -3397,10 +3385,10 @@
         <v>29</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3417,7 +3405,7 @@
         <v>29</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>21</v>
@@ -3437,7 +3425,7 @@
         <v>29</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>21</v>
@@ -3457,7 +3445,7 @@
         <v>29</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>21</v>
@@ -3477,10 +3465,10 @@
         <v>29</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3497,10 +3485,10 @@
         <v>29</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3517,7 +3505,7 @@
         <v>29</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3525,10 +3513,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3537,18 +3525,18 @@
         <v>29</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>70</v>
+        <v>244</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3557,18 +3545,18 @@
         <v>29</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3577,7 +3565,7 @@
         <v>29</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>21</v>
@@ -3585,10 +3573,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3597,7 +3585,7 @@
         <v>29</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>21</v>
@@ -3605,10 +3593,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3617,7 +3605,7 @@
         <v>29</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>21</v>
@@ -3634,10 +3622,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>254</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>21</v>
@@ -3654,10 +3642,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>254</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>21</v>
@@ -3677,7 +3665,7 @@
         <v>34</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>21</v>
@@ -3697,7 +3685,7 @@
         <v>34</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>21</v>
@@ -3717,7 +3705,7 @@
         <v>34</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>21</v>
@@ -3737,10 +3725,10 @@
         <v>34</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3757,7 +3745,7 @@
         <v>34</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>21</v>
@@ -3777,7 +3765,7 @@
         <v>34</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3797,7 +3785,7 @@
         <v>34</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>21</v>
@@ -3817,10 +3805,10 @@
         <v>34</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3837,7 +3825,7 @@
         <v>34</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>21</v>
@@ -3860,46 +3848,6 @@
         <v>34</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F132" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/STA01D.xlsx
+++ b/STA01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="275">
   <si>
     <t/>
   </si>
@@ -211,439 +211,427 @@
     <t>11</t>
   </si>
   <si>
-    <t>20137071</t>
-  </si>
-  <si>
-    <t>CRAYOLA SCRIBBLE PET</t>
+    <t>10022100</t>
+  </si>
+  <si>
+    <t>SINDU ORIGAMI 100S B</t>
+  </si>
+  <si>
+    <t>10022101</t>
+  </si>
+  <si>
+    <t>SINDU ORIGAMI 100S T</t>
+  </si>
+  <si>
+    <t>20122345</t>
+  </si>
+  <si>
+    <t>DELI PAPER CLIP 0024</t>
+  </si>
+  <si>
+    <t>20126392</t>
+  </si>
+  <si>
+    <t>PSTIT SS NT FLA 135S</t>
+  </si>
+  <si>
+    <t>20036265</t>
+  </si>
+  <si>
+    <t>JOYKO GLUE STIK GS15</t>
+  </si>
+  <si>
+    <t>20122425</t>
+  </si>
+  <si>
+    <t>JOYKO TWIST CRYN 12S</t>
+  </si>
+  <si>
+    <t>20137691</t>
+  </si>
+  <si>
+    <t>ADINATA PENC.TROP M3</t>
+  </si>
+  <si>
+    <t>20138868</t>
+  </si>
+  <si>
+    <t>RHINO DIY BEAD CHARM</t>
+  </si>
+  <si>
+    <t>20132581</t>
+  </si>
+  <si>
+    <t>STNRY ICE CRM ERASER</t>
+  </si>
+  <si>
+    <t>20136257</t>
+  </si>
+  <si>
+    <t>STNRY SEA ANIMAL PEN</t>
+  </si>
+  <si>
+    <t>20136258</t>
+  </si>
+  <si>
+    <t>STNRY DRAGON PEN</t>
+  </si>
+  <si>
+    <t>20136260</t>
+  </si>
+  <si>
+    <t>STNRY DIY PNCL 2B 3S</t>
+  </si>
+  <si>
+    <t>20136261</t>
+  </si>
+  <si>
+    <t>STNRY DIY BRCK RULER</t>
+  </si>
+  <si>
+    <t>20136262</t>
+  </si>
+  <si>
+    <t>STNRY DIY BRCK SHRPN</t>
+  </si>
+  <si>
+    <t>20139864</t>
+  </si>
+  <si>
+    <t>STNRY HP DUCK ERASER</t>
+  </si>
+  <si>
+    <t>20139865</t>
+  </si>
+  <si>
+    <t>STNRY FST FD GLU STK</t>
+  </si>
+  <si>
+    <t>20139866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STNRY SMR FRUIT PEN </t>
+  </si>
+  <si>
+    <t>20139867</t>
+  </si>
+  <si>
+    <t>STNRY ICE/C PUSH PEN</t>
+  </si>
+  <si>
+    <t>20139868</t>
+  </si>
+  <si>
+    <t>STNRY FAST FOOD PEN</t>
+  </si>
+  <si>
+    <t>20139869</t>
+  </si>
+  <si>
+    <t>STNRY CMERA TOPR PEN</t>
+  </si>
+  <si>
+    <t>20139871</t>
+  </si>
+  <si>
+    <t>STNRY FASTN FD PNCIL</t>
+  </si>
+  <si>
+    <t>20139873</t>
+  </si>
+  <si>
+    <t>STNRY SUMMER RULER</t>
+  </si>
+  <si>
+    <t>20139874</t>
+  </si>
+  <si>
+    <t>STNRY FAST FD SHARPN</t>
+  </si>
+  <si>
+    <t>20139881</t>
+  </si>
+  <si>
+    <t>STNRY LIT.STICK NOTE</t>
+  </si>
+  <si>
+    <t>20105929</t>
+  </si>
+  <si>
+    <t>STNRY VGTBLE 3D PEN</t>
+  </si>
+  <si>
+    <t>20133801</t>
+  </si>
+  <si>
+    <t>ADNTA SCRET PEN MIX2</t>
+  </si>
+  <si>
+    <t>20137049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADNTA PEN W/TOPPER  </t>
+  </si>
+  <si>
+    <t>20137050</t>
+  </si>
+  <si>
+    <t>ADNTA GEL PEN RUBBER</t>
+  </si>
+  <si>
+    <t>20128687</t>
+  </si>
+  <si>
+    <t>ADNTA M/MNI NOTES 3S</t>
+  </si>
+  <si>
+    <t>20137718</t>
+  </si>
+  <si>
+    <t>STNRY RABBIT ERASER</t>
+  </si>
+  <si>
+    <t>20137719</t>
+  </si>
+  <si>
+    <t>STNRY PEN CUTE TROPR</t>
+  </si>
+  <si>
+    <t>20137720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STNRY CACTUS GLUE </t>
+  </si>
+  <si>
+    <t>20055289</t>
+  </si>
+  <si>
+    <t>A/N STICKER  PUFFY</t>
+  </si>
+  <si>
+    <t>20093329</t>
+  </si>
+  <si>
+    <t>DELI SCISSORS 6021</t>
+  </si>
+  <si>
+    <t>20098010</t>
+  </si>
+  <si>
+    <t>ADNTA NOTE STAT.MIX1</t>
+  </si>
+  <si>
+    <t>20098390</t>
+  </si>
+  <si>
+    <t>DELI GLUE STCK 6366A</t>
+  </si>
+  <si>
+    <t>20098391</t>
+  </si>
+  <si>
+    <t>DELI CRCT PEN H10200</t>
+  </si>
+  <si>
+    <t>20098398</t>
+  </si>
+  <si>
+    <t>DELI PR.MRKR BLU&amp;BLC</t>
+  </si>
+  <si>
+    <t>20098406</t>
+  </si>
+  <si>
+    <t>DELI CTTER 2022/2024</t>
+  </si>
+  <si>
+    <t>20132577</t>
+  </si>
+  <si>
+    <t>STNRY ORGMI DUCK PEN</t>
+  </si>
+  <si>
+    <t>20138869</t>
+  </si>
+  <si>
+    <t>RHINO CHRYSTAL WHIMP</t>
+  </si>
+  <si>
+    <t>20138874</t>
+  </si>
+  <si>
+    <t>RHINO BUBBLE TEA</t>
+  </si>
+  <si>
+    <t>20052056</t>
+  </si>
+  <si>
+    <t>STICKER 12.500 PCS</t>
+  </si>
+  <si>
+    <t>20057932</t>
+  </si>
+  <si>
+    <t>STICKER GIRLS</t>
+  </si>
+  <si>
+    <t>20085048</t>
+  </si>
+  <si>
+    <t>A/N STCKR BOOK 7 SCN</t>
+  </si>
+  <si>
+    <t>20096351</t>
+  </si>
+  <si>
+    <t>ADNTA STCKR ML.PONY</t>
+  </si>
+  <si>
+    <t>20130761</t>
+  </si>
+  <si>
+    <t>ADINATA EMBSD STCKER</t>
+  </si>
+  <si>
+    <t>20130762</t>
+  </si>
+  <si>
+    <t>ADINATA SHKER STCKER</t>
+  </si>
+  <si>
+    <t>20130795</t>
+  </si>
+  <si>
+    <t>RHINO STICKER ASTD</t>
+  </si>
+  <si>
+    <t>20132476</t>
+  </si>
+  <si>
+    <t>DADI SHAKING STICKER</t>
+  </si>
+  <si>
+    <t>20132477</t>
+  </si>
+  <si>
+    <t>DADI DIY STICKER</t>
+  </si>
+  <si>
+    <t>20133141</t>
+  </si>
+  <si>
+    <t>RHINO STICKER PUFFY</t>
+  </si>
+  <si>
+    <t>20135718</t>
+  </si>
+  <si>
+    <t>CPCRN STCKR PCK ASST</t>
+  </si>
+  <si>
+    <t>20136100</t>
+  </si>
+  <si>
+    <t>RHINO STICKER FAMILY</t>
+  </si>
+  <si>
+    <t>20136249</t>
+  </si>
+  <si>
+    <t>DADI DIY STCKR PLYST</t>
+  </si>
+  <si>
+    <t>20136853</t>
+  </si>
+  <si>
+    <t>ADINATA DC/FELT STKR</t>
+  </si>
+  <si>
+    <t>20136854</t>
+  </si>
+  <si>
+    <t>ADINATA JELY STICKER</t>
+  </si>
+  <si>
+    <t>20137074</t>
+  </si>
+  <si>
+    <t>ADINATA FRAME STICKR</t>
+  </si>
+  <si>
+    <t>20137075</t>
+  </si>
+  <si>
+    <t>ADINATA DIY ST STCKR</t>
+  </si>
+  <si>
+    <t>20137098</t>
+  </si>
+  <si>
+    <t>RHINO STICKER KANAMA</t>
+  </si>
+  <si>
+    <t>10022333</t>
+  </si>
+  <si>
+    <t>SNOWMAN SPD KCL 3'S</t>
+  </si>
+  <si>
+    <t>10024555</t>
+  </si>
+  <si>
+    <t>F/C PAKET UMPTN SET</t>
+  </si>
+  <si>
+    <t>20032859</t>
+  </si>
+  <si>
+    <t>DADI PVC PENCASE+</t>
+  </si>
+  <si>
+    <t>20137292</t>
+  </si>
+  <si>
+    <t>IDM GEL PEN 3'S</t>
+  </si>
+  <si>
+    <t>20128379</t>
+  </si>
+  <si>
+    <t>KENKO G.PEN+LGHTR 2S</t>
+  </si>
+  <si>
+    <t>10010596</t>
+  </si>
+  <si>
+    <t>F/C PENCIL WN 114462</t>
+  </si>
+  <si>
+    <t>10011819</t>
+  </si>
+  <si>
+    <t>SNOWMAN SPDL WRN 12S</t>
+  </si>
+  <si>
+    <t>20012674</t>
+  </si>
+  <si>
+    <t>ADINATA STTIONARY 7S</t>
+  </si>
+  <si>
+    <t>20130763</t>
+  </si>
+  <si>
+    <t>KENKO CR.TAPE CT-902</t>
+  </si>
+  <si>
+    <t>20129005</t>
+  </si>
+  <si>
+    <t>EMCO FUN WITH COLORS</t>
   </si>
   <si>
     <t>12</t>
-  </si>
-  <si>
-    <t>10022100</t>
-  </si>
-  <si>
-    <t>SINDU ORIGAMI 100S B</t>
-  </si>
-  <si>
-    <t>10022101</t>
-  </si>
-  <si>
-    <t>SINDU ORIGAMI 100S T</t>
-  </si>
-  <si>
-    <t>20122345</t>
-  </si>
-  <si>
-    <t>DELI PAPER CLIP 0024</t>
-  </si>
-  <si>
-    <t>20126392</t>
-  </si>
-  <si>
-    <t>PSTIT SS NT FLA 135S</t>
-  </si>
-  <si>
-    <t>20036265</t>
-  </si>
-  <si>
-    <t>JOYKO GLUE STIK GS15</t>
-  </si>
-  <si>
-    <t>20122425</t>
-  </si>
-  <si>
-    <t>JOYKO TWIST CRYN 12S</t>
-  </si>
-  <si>
-    <t>20137691</t>
-  </si>
-  <si>
-    <t>ADINATA PENC.TROP M3</t>
-  </si>
-  <si>
-    <t>20138868</t>
-  </si>
-  <si>
-    <t>RHINO DIY BEAD CHARM</t>
-  </si>
-  <si>
-    <t>20132581</t>
-  </si>
-  <si>
-    <t>STNRY ICE CRM ERASER</t>
-  </si>
-  <si>
-    <t>20136257</t>
-  </si>
-  <si>
-    <t>STNRY SEA ANIMAL PEN</t>
-  </si>
-  <si>
-    <t>20136258</t>
-  </si>
-  <si>
-    <t>STNRY DRAGON PEN</t>
-  </si>
-  <si>
-    <t>20136260</t>
-  </si>
-  <si>
-    <t>STNRY DIY PNCL 2B 3S</t>
-  </si>
-  <si>
-    <t>20136261</t>
-  </si>
-  <si>
-    <t>STNRY DIY BRCK RULER</t>
-  </si>
-  <si>
-    <t>20136262</t>
-  </si>
-  <si>
-    <t>STNRY DIY BRCK SHRPN</t>
-  </si>
-  <si>
-    <t>20139864</t>
-  </si>
-  <si>
-    <t>STNRY HP DUCK ERASER</t>
-  </si>
-  <si>
-    <t>20139865</t>
-  </si>
-  <si>
-    <t>STNRY FST FD GLU STK</t>
-  </si>
-  <si>
-    <t>20139866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STNRY SMR FRUIT PEN </t>
-  </si>
-  <si>
-    <t>20139867</t>
-  </si>
-  <si>
-    <t>STNRY ICE/C PUSH PEN</t>
-  </si>
-  <si>
-    <t>20139868</t>
-  </si>
-  <si>
-    <t>STNRY FAST FOOD PEN</t>
-  </si>
-  <si>
-    <t>20139869</t>
-  </si>
-  <si>
-    <t>STNRY CMERA TOPR PEN</t>
-  </si>
-  <si>
-    <t>20139871</t>
-  </si>
-  <si>
-    <t>STNRY FASTN FD PNCIL</t>
-  </si>
-  <si>
-    <t>20139873</t>
-  </si>
-  <si>
-    <t>STNRY SUMMER RULER</t>
-  </si>
-  <si>
-    <t>20139874</t>
-  </si>
-  <si>
-    <t>STNRY FAST FD SHARPN</t>
-  </si>
-  <si>
-    <t>20139881</t>
-  </si>
-  <si>
-    <t>STNRY LIT.STICK NOTE</t>
-  </si>
-  <si>
-    <t>20105929</t>
-  </si>
-  <si>
-    <t>STNRY VGTBLE 3D PEN</t>
-  </si>
-  <si>
-    <t>20133801</t>
-  </si>
-  <si>
-    <t>ADNTA SCRET PEN MIX2</t>
-  </si>
-  <si>
-    <t>20137049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADNTA PEN W/TOPPER  </t>
-  </si>
-  <si>
-    <t>20137050</t>
-  </si>
-  <si>
-    <t>ADNTA GEL PEN RUBBER</t>
-  </si>
-  <si>
-    <t>20128687</t>
-  </si>
-  <si>
-    <t>ADNTA M/MNI NOTES 3S</t>
-  </si>
-  <si>
-    <t>20137718</t>
-  </si>
-  <si>
-    <t>STNRY RABBIT ERASER</t>
-  </si>
-  <si>
-    <t>20137719</t>
-  </si>
-  <si>
-    <t>STNRY PEN CUTE TROPR</t>
-  </si>
-  <si>
-    <t>20137720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STNRY CACTUS GLUE </t>
-  </si>
-  <si>
-    <t>20055289</t>
-  </si>
-  <si>
-    <t>A/N STICKER  PUFFY</t>
-  </si>
-  <si>
-    <t>20093329</t>
-  </si>
-  <si>
-    <t>DELI SCISSORS 6021</t>
-  </si>
-  <si>
-    <t>20098010</t>
-  </si>
-  <si>
-    <t>ADNTA NOTE STAT.MIX1</t>
-  </si>
-  <si>
-    <t>20098390</t>
-  </si>
-  <si>
-    <t>DELI GLUE STCK 6366A</t>
-  </si>
-  <si>
-    <t>20098391</t>
-  </si>
-  <si>
-    <t>DELI CRCT PEN H10200</t>
-  </si>
-  <si>
-    <t>20098398</t>
-  </si>
-  <si>
-    <t>DELI PR.MRKR BLU&amp;BLC</t>
-  </si>
-  <si>
-    <t>20098406</t>
-  </si>
-  <si>
-    <t>DELI CTTER 2022/2024</t>
-  </si>
-  <si>
-    <t>20132577</t>
-  </si>
-  <si>
-    <t>STNRY ORGMI DUCK PEN</t>
-  </si>
-  <si>
-    <t>20138869</t>
-  </si>
-  <si>
-    <t>RHINO CHRYSTAL WHIMP</t>
-  </si>
-  <si>
-    <t>20138874</t>
-  </si>
-  <si>
-    <t>RHINO BUBBLE TEA</t>
-  </si>
-  <si>
-    <t>20052056</t>
-  </si>
-  <si>
-    <t>STICKER 12.500 PCS</t>
-  </si>
-  <si>
-    <t>20057932</t>
-  </si>
-  <si>
-    <t>STICKER GIRLS</t>
-  </si>
-  <si>
-    <t>20085048</t>
-  </si>
-  <si>
-    <t>A/N STCKR BOOK 7 SCN</t>
-  </si>
-  <si>
-    <t>20096351</t>
-  </si>
-  <si>
-    <t>ADNTA STCKR ML.PONY</t>
-  </si>
-  <si>
-    <t>20130761</t>
-  </si>
-  <si>
-    <t>ADINATA EMBSD STCKER</t>
-  </si>
-  <si>
-    <t>20130762</t>
-  </si>
-  <si>
-    <t>ADINATA SHKER STCKER</t>
-  </si>
-  <si>
-    <t>20130795</t>
-  </si>
-  <si>
-    <t>RHINO STICKER ASTD</t>
-  </si>
-  <si>
-    <t>20132476</t>
-  </si>
-  <si>
-    <t>DADI SHAKING STICKER</t>
-  </si>
-  <si>
-    <t>20132477</t>
-  </si>
-  <si>
-    <t>DADI DIY STICKER</t>
-  </si>
-  <si>
-    <t>20133141</t>
-  </si>
-  <si>
-    <t>RHINO STICKER PUFFY</t>
-  </si>
-  <si>
-    <t>20135718</t>
-  </si>
-  <si>
-    <t>CPCRN STCKR PCK ASST</t>
-  </si>
-  <si>
-    <t>20136100</t>
-  </si>
-  <si>
-    <t>RHINO STICKER FAMILY</t>
-  </si>
-  <si>
-    <t>20136249</t>
-  </si>
-  <si>
-    <t>DADI DIY STCKR PLYST</t>
-  </si>
-  <si>
-    <t>20136853</t>
-  </si>
-  <si>
-    <t>ADINATA DC/FELT STKR</t>
-  </si>
-  <si>
-    <t>20136854</t>
-  </si>
-  <si>
-    <t>ADINATA JELY STICKER</t>
-  </si>
-  <si>
-    <t>20137074</t>
-  </si>
-  <si>
-    <t>ADINATA FRAME STICKR</t>
-  </si>
-  <si>
-    <t>20137075</t>
-  </si>
-  <si>
-    <t>ADINATA DIY ST STCKR</t>
-  </si>
-  <si>
-    <t>20137098</t>
-  </si>
-  <si>
-    <t>RHINO STICKER KANAMA</t>
-  </si>
-  <si>
-    <t>10022333</t>
-  </si>
-  <si>
-    <t>SNOWMAN SPD KCL 3'S</t>
-  </si>
-  <si>
-    <t>10024555</t>
-  </si>
-  <si>
-    <t>F/C PAKET UMPTN SET</t>
-  </si>
-  <si>
-    <t>20123565</t>
-  </si>
-  <si>
-    <t>F/C PAKET MENULIS</t>
-  </si>
-  <si>
-    <t>20032859</t>
-  </si>
-  <si>
-    <t>DADI PVC PENCASE+</t>
-  </si>
-  <si>
-    <t>20137292</t>
-  </si>
-  <si>
-    <t>IDM GEL PEN 3'S</t>
-  </si>
-  <si>
-    <t>20128379</t>
-  </si>
-  <si>
-    <t>KENKO G.PEN+LGHTR 2S</t>
-  </si>
-  <si>
-    <t>10010596</t>
-  </si>
-  <si>
-    <t>F/C PENCIL WN 114462</t>
-  </si>
-  <si>
-    <t>10011819</t>
-  </si>
-  <si>
-    <t>SNOWMAN SPDL WRN 12S</t>
-  </si>
-  <si>
-    <t>20012674</t>
-  </si>
-  <si>
-    <t>ADINATA STTIONARY 7S</t>
-  </si>
-  <si>
-    <t>20130763</t>
-  </si>
-  <si>
-    <t>KENKO CR.TAPE CT-902</t>
-  </si>
-  <si>
-    <t>20129005</t>
-  </si>
-  <si>
-    <t>EMCO FUN WITH COLORS</t>
   </si>
   <si>
     <t>10038449</t>
@@ -1240,7 +1228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1782,21 +1770,21 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1813,10 +1801,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1825,7 +1813,7 @@
         <v>17</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>21</v>
@@ -1833,10 +1821,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1845,7 +1833,7 @@
         <v>17</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>21</v>
@@ -1853,10 +1841,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1865,7 +1853,7 @@
         <v>17</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>21</v>
@@ -1873,10 +1861,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1885,7 +1873,7 @@
         <v>17</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>21</v>
@@ -1893,10 +1881,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1905,7 +1893,7 @@
         <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>21</v>
@@ -1913,10 +1901,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1925,7 +1913,7 @@
         <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>21</v>
@@ -1933,30 +1921,30 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1973,10 +1961,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1993,10 +1981,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2013,10 +2001,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2033,10 +2021,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2053,10 +2041,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2073,10 +2061,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2093,10 +2081,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2113,10 +2101,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2133,10 +2121,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2153,10 +2141,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2173,10 +2161,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2193,10 +2181,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2213,10 +2201,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2233,10 +2221,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2253,11 +2241,11 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
@@ -2265,7 +2253,7 @@
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2273,11 +2261,11 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
@@ -2285,18 +2273,18 @@
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2313,10 +2301,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2333,11 +2321,11 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
@@ -2345,7 +2333,7 @@
         <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>21</v>
@@ -2353,10 +2341,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2368,15 +2356,15 @@
         <v>24</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2393,10 +2381,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2413,11 +2401,11 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
@@ -2425,18 +2413,18 @@
         <v>20</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2453,10 +2441,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2473,10 +2461,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2493,10 +2481,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2513,10 +2501,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2533,10 +2521,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2553,11 +2541,11 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
@@ -2565,19 +2553,19 @@
         <v>20</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
@@ -2585,18 +2573,18 @@
         <v>20</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2613,11 +2601,11 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
@@ -2625,7 +2613,7 @@
         <v>20</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>21</v>
@@ -2633,10 +2621,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -2653,10 +2641,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -2673,10 +2661,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2693,10 +2681,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2713,10 +2701,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2733,10 +2721,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2753,10 +2741,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2773,10 +2761,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2793,10 +2781,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2813,10 +2801,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2833,10 +2821,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2853,10 +2841,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2873,10 +2861,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2888,15 +2876,15 @@
         <v>59</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2913,10 +2901,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -2928,15 +2916,15 @@
         <v>59</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -2953,10 +2941,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -2973,19 +2961,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>21</v>
@@ -2993,10 +2981,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3005,7 +2993,7 @@
         <v>24</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>21</v>
@@ -3013,10 +3001,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3025,7 +3013,7 @@
         <v>24</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>21</v>
@@ -3033,10 +3021,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3045,7 +3033,7 @@
         <v>24</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>21</v>
@@ -3053,10 +3041,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3065,7 +3053,7 @@
         <v>24</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>21</v>
@@ -3073,10 +3061,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3085,7 +3073,7 @@
         <v>24</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>21</v>
@@ -3093,10 +3081,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3105,7 +3093,7 @@
         <v>24</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>21</v>
@@ -3113,10 +3101,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3125,7 +3113,7 @@
         <v>24</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>21</v>
@@ -3133,10 +3121,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3145,7 +3133,7 @@
         <v>24</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>21</v>
@@ -3153,10 +3141,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3165,10 +3153,10 @@
         <v>24</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3182,10 +3170,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>21</v>
@@ -3202,13 +3190,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3225,7 +3213,7 @@
         <v>29</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>21</v>
@@ -3245,7 +3233,7 @@
         <v>29</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>21</v>
@@ -3265,7 +3253,7 @@
         <v>29</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>21</v>
@@ -3285,7 +3273,7 @@
         <v>29</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>21</v>
@@ -3305,10 +3293,10 @@
         <v>29</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3325,7 +3313,7 @@
         <v>29</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>21</v>
@@ -3345,10 +3333,10 @@
         <v>29</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3365,7 +3353,7 @@
         <v>29</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>21</v>
@@ -3385,7 +3373,7 @@
         <v>29</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>21</v>
@@ -3405,7 +3393,7 @@
         <v>29</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>21</v>
@@ -3425,10 +3413,10 @@
         <v>29</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3445,10 +3433,10 @@
         <v>29</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3465,7 +3453,7 @@
         <v>29</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>65</v>
+        <v>237</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3473,10 +3461,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3485,18 +3473,18 @@
         <v>29</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>68</v>
+        <v>240</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3505,18 +3493,18 @@
         <v>29</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3525,7 +3513,7 @@
         <v>29</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>21</v>
@@ -3533,10 +3521,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3545,7 +3533,7 @@
         <v>29</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>21</v>
@@ -3553,10 +3541,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3565,7 +3553,7 @@
         <v>29</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>21</v>
@@ -3582,10 +3570,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>21</v>
@@ -3602,10 +3590,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>21</v>
@@ -3625,7 +3613,7 @@
         <v>34</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>21</v>
@@ -3645,7 +3633,7 @@
         <v>34</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>21</v>
@@ -3665,7 +3653,7 @@
         <v>34</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>21</v>
@@ -3685,10 +3673,10 @@
         <v>34</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3705,7 +3693,7 @@
         <v>34</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>21</v>
@@ -3725,7 +3713,7 @@
         <v>34</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3745,7 +3733,7 @@
         <v>34</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>21</v>
@@ -3765,10 +3753,10 @@
         <v>34</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3785,7 +3773,7 @@
         <v>34</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>21</v>
@@ -3808,46 +3796,6 @@
         <v>34</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F130" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/STA01D.xlsx
+++ b/STA01D.xlsx
@@ -181,7 +181,7 @@
     <t>LARISST SPR GLUE 10G</t>
   </si>
   <si>
-    <t>PT,(E-24B)</t>
+    <t>PT,(E-1B)</t>
   </si>
   <si>
     <t>10000656</t>
@@ -1236,7 +1236,7 @@
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
